--- a/excel/Grille de compétence  - BTS SIO 2026 (4).xlsx
+++ b/excel/Grille de compétence  - BTS SIO 2026 (4).xlsx
@@ -8,19 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projet portfolio\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78FAC9B1-BF20-4B09-9B6C-2784AF11CCF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60EFA77-B4C4-499F-B384-16954B6D5449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="35EqtO/En8jRpbiYLcV3cjaU+lDk3ZfqPG/5qKSy5nA="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -48,30 +43,10 @@
     <t>Option :</t>
   </si>
   <si>
-    <t>▢  SISR</t>
+    <t>▣  SISR</t>
   </si>
   <si>
     <t>▢ SLAM</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="18"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t xml:space="preserve">Adresse URL du portfolio : </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="18"/>
-        <color rgb="FF1155CC"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>https://sites.google.com/view/portfoliodamara/accueil</t>
-    </r>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -224,6 +199,9 @@
   <si>
     <t>Formater un disque dur système</t>
   </si>
+  <si>
+    <t>Adresse URL du portfolio : https://amaraybk.github.io/Portfolio-Amara/#bts</t>
+  </si>
 </sst>
 </file>
 
@@ -232,7 +210,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/yyyy"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -253,18 +231,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
-      <sz val="18"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -315,16 +282,19 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <u/>
-      <sz val="18"/>
-      <color rgb="FF1155CC"/>
+      <sz val="20"/>
+      <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -341,19 +311,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -381,37 +338,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF494429"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color rgb="FF494429"/>
       </right>
       <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right/>
-      <top style="thin">
         <color rgb="FF494429"/>
       </top>
       <bottom style="thin">
@@ -470,19 +401,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF494429"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -508,19 +426,6 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="FF494429"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF494429"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF494429"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF494429"/>
       </left>
       <right style="thin">
@@ -702,137 +607,223 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF494429"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF494429"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF494429"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF494429"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF494429"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF494429"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF494429"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF494429"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF494429"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF494429"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF494429"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF494429"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF494429"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF494429"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF494429"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF494429"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF494429"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF494429"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF494429"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF494429"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1059,56 +1050,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="42" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="43"/>
+      <c r="H1" s="39"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="44" t="s">
+      <c r="A3" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="46" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="37"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="42"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="47" t="s">
+      <c r="A4" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="48"/>
+      <c r="B4" s="34"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1119,106 +1110,106 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="49" t="s">
+    <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="52"/>
+    </row>
+    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="51"/>
-    </row>
-    <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="32" t="s">
+      <c r="B6" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="C6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:13" ht="324.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="47"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="324.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="33"/>
-      <c r="B7" s="35"/>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="45" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="36" t="s">
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
+    </row>
+    <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="38"/>
-    </row>
-    <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+      <c r="B9" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="C9" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>27</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+      <c r="B10" s="31" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -1226,18 +1217,18 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>31</v>
-      </c>
       <c r="C11" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
@@ -1247,13 +1238,13 @@
     </row>
     <row r="12" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>33</v>
-      </c>
       <c r="C12" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
@@ -1263,19 +1254,19 @@
     </row>
     <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>35</v>
-      </c>
       <c r="C13" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H13" s="12"/>
     </row>
@@ -1320,29 +1311,29 @@
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="39" t="s">
+      <c r="A18" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="35"/>
+    </row>
+    <row r="19" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="41"/>
-    </row>
-    <row r="19" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
+      <c r="B19" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="15" t="s">
-        <v>27</v>
+      <c r="C19" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="16"/>
@@ -1351,49 +1342,49 @@
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="54" t="s">
         <v>39</v>
-      </c>
-      <c r="B20" s="18" t="s">
-        <v>40</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="53" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="15" t="s">
-        <v>27</v>
+      <c r="C21" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="18" t="s">
-        <v>44</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -1402,17 +1393,17 @@
       <c r="H22" s="17"/>
     </row>
     <row r="23" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>46</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="16"/>
@@ -1420,7 +1411,7 @@
       <c r="H23" s="17"/>
     </row>
     <row r="24" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="19"/>
+      <c r="A24" s="18"/>
       <c r="B24" s="15"/>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -1430,7 +1421,7 @@
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="20"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="15"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -1440,29 +1431,29 @@
       <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="39" t="s">
+      <c r="A26" s="33" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="35"/>
+    </row>
+    <row r="27" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="40"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="41"/>
-    </row>
-    <row r="27" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="9" t="s">
+      <c r="B27" s="53" t="s">
         <v>48</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="15" t="s">
-        <v>27</v>
+      <c r="C27" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
@@ -1471,49 +1462,49 @@
     </row>
     <row r="28" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
-      <c r="B28" s="18">
+      <c r="B28" s="54">
         <v>46023</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H28" s="17"/>
     </row>
     <row r="29" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>27</v>
+      <c r="C29" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="H29" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
-        <v>53</v>
+      <c r="A30" s="18" t="s">
+        <v>52</v>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="54">
         <v>46023</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
@@ -1522,7 +1513,7 @@
       <c r="H30" s="17"/>
     </row>
     <row r="31" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="21"/>
+      <c r="A31" s="20"/>
       <c r="B31" s="15"/>
       <c r="C31" s="11"/>
       <c r="D31" s="11"/>
@@ -1532,7 +1523,7 @@
       <c r="H31" s="17"/>
     </row>
     <row r="32" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="15"/>
       <c r="C32" s="11"/>
       <c r="D32" s="11"/>
@@ -1542,30 +1533,30 @@
       <c r="H32" s="17"/>
     </row>
     <row r="33" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="26"/>
-      <c r="H33" s="27"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="26"/>
     </row>
     <row r="34" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="28"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
-      <c r="E34" s="30"/>
-      <c r="F34" s="30"/>
-      <c r="G34" s="30"/>
-      <c r="H34" s="30"/>
+      <c r="A34" s="27"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
     </row>
     <row r="35" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
-      <c r="D35" s="31"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -1575,7 +1566,7 @@
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-      <c r="D36" s="31"/>
+      <c r="D36" s="30"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1585,7 +1576,7 @@
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
-      <c r="D37" s="31"/>
+      <c r="D37" s="30"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1595,7 +1586,7 @@
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
-      <c r="D38" s="31"/>
+      <c r="D38" s="30"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -1605,7 +1596,7 @@
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
-      <c r="D39" s="31"/>
+      <c r="D39" s="30"/>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -1615,7 +1606,7 @@
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
-      <c r="D40" s="31"/>
+      <c r="D40" s="30"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -1625,7 +1616,7 @@
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
-      <c r="D41" s="31"/>
+      <c r="D41" s="30"/>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -1635,7 +1626,7 @@
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
-      <c r="D42" s="31"/>
+      <c r="D42" s="30"/>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
@@ -1645,7 +1636,7 @@
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
-      <c r="D43" s="31"/>
+      <c r="D43" s="30"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
@@ -1655,7 +1646,7 @@
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
-      <c r="D44" s="31"/>
+      <c r="D44" s="30"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
@@ -1665,7 +1656,7 @@
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
-      <c r="D45" s="31"/>
+      <c r="D45" s="30"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
@@ -1675,7 +1666,7 @@
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
-      <c r="D46" s="31"/>
+      <c r="D46" s="30"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
@@ -1685,7 +1676,7 @@
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
-      <c r="D47" s="31"/>
+      <c r="D47" s="30"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
@@ -1695,7 +1686,7 @@
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
-      <c r="D48" s="31"/>
+      <c r="D48" s="30"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
@@ -1705,7 +1696,7 @@
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
-      <c r="D49" s="31"/>
+      <c r="D49" s="30"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -1715,7 +1706,7 @@
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
-      <c r="D50" s="31"/>
+      <c r="D50" s="30"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
@@ -1725,7 +1716,7 @@
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
-      <c r="D51" s="31"/>
+      <c r="D51" s="30"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
@@ -1735,7 +1726,7 @@
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
-      <c r="D52" s="31"/>
+      <c r="D52" s="30"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
@@ -1745,7 +1736,7 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="31"/>
+      <c r="D53" s="30"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -1755,7 +1746,7 @@
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
-      <c r="D54" s="31"/>
+      <c r="D54" s="30"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -1765,7 +1756,7 @@
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
-      <c r="D55" s="31"/>
+      <c r="D55" s="30"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -1775,7 +1766,7 @@
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
-      <c r="D56" s="31"/>
+      <c r="D56" s="30"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -1785,7 +1776,7 @@
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
-      <c r="D57" s="31"/>
+      <c r="D57" s="30"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -1795,7 +1786,7 @@
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
-      <c r="D58" s="31"/>
+      <c r="D58" s="30"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -1805,7 +1796,7 @@
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
-      <c r="D59" s="31"/>
+      <c r="D59" s="30"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
@@ -1815,7 +1806,7 @@
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
-      <c r="D60" s="31"/>
+      <c r="D60" s="30"/>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
@@ -1825,7 +1816,7 @@
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
-      <c r="D61" s="31"/>
+      <c r="D61" s="30"/>
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
@@ -1835,7 +1826,7 @@
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
-      <c r="D62" s="31"/>
+      <c r="D62" s="30"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
@@ -1845,7 +1836,7 @@
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
-      <c r="D63" s="31"/>
+      <c r="D63" s="30"/>
       <c r="E63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
@@ -1855,7 +1846,7 @@
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
-      <c r="D64" s="31"/>
+      <c r="D64" s="30"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -1865,7 +1856,7 @@
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
-      <c r="D65" s="31"/>
+      <c r="D65" s="30"/>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
       <c r="G65" s="1"/>
@@ -1875,7 +1866,7 @@
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
-      <c r="D66" s="31"/>
+      <c r="D66" s="30"/>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
       <c r="G66" s="1"/>
@@ -1885,7 +1876,7 @@
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
-      <c r="D67" s="31"/>
+      <c r="D67" s="30"/>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
@@ -1895,7 +1886,7 @@
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
-      <c r="D68" s="31"/>
+      <c r="D68" s="30"/>
       <c r="E68" s="1"/>
       <c r="F68" s="1"/>
       <c r="G68" s="1"/>
@@ -1905,7 +1896,7 @@
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
-      <c r="D69" s="31"/>
+      <c r="D69" s="30"/>
       <c r="E69" s="1"/>
       <c r="F69" s="1"/>
       <c r="G69" s="1"/>
@@ -1915,7 +1906,7 @@
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
-      <c r="D70" s="31"/>
+      <c r="D70" s="30"/>
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
       <c r="G70" s="1"/>
@@ -1925,7 +1916,7 @@
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
-      <c r="D71" s="31"/>
+      <c r="D71" s="30"/>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
@@ -1935,7 +1926,7 @@
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
-      <c r="D72" s="31"/>
+      <c r="D72" s="30"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -1945,7 +1936,7 @@
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
-      <c r="D73" s="31"/>
+      <c r="D73" s="30"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
@@ -1955,7 +1946,7 @@
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
-      <c r="D74" s="31"/>
+      <c r="D74" s="30"/>
       <c r="E74" s="1"/>
       <c r="F74" s="1"/>
       <c r="G74" s="1"/>
@@ -1965,7 +1956,7 @@
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
-      <c r="D75" s="31"/>
+      <c r="D75" s="30"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1"/>
       <c r="G75" s="1"/>
@@ -1975,7 +1966,7 @@
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
-      <c r="D76" s="31"/>
+      <c r="D76" s="30"/>
       <c r="E76" s="1"/>
       <c r="F76" s="1"/>
       <c r="G76" s="1"/>
@@ -1985,7 +1976,7 @@
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
-      <c r="D77" s="31"/>
+      <c r="D77" s="30"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -1995,7 +1986,7 @@
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
-      <c r="D78" s="31"/>
+      <c r="D78" s="30"/>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
       <c r="G78" s="1"/>
@@ -2005,7 +1996,7 @@
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
-      <c r="D79" s="31"/>
+      <c r="D79" s="30"/>
       <c r="E79" s="1"/>
       <c r="F79" s="1"/>
       <c r="G79" s="1"/>
@@ -2015,7 +2006,7 @@
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
-      <c r="D80" s="31"/>
+      <c r="D80" s="30"/>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -11213,21 +11204,22 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:H2"/>
     <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A5" r:id="rId1" display="Adresse URL du portfolio : https://amaraybk.github.io/Portfolio-Amara/" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A5:H5" r:id="rId2" location="bts" display="Adresse URL du portfolio : https://amaraybk.github.io/Portfolio-Amara/#bts" xr:uid="{B63E0153-DF23-4497-BB23-44008073AC47}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0" footer="0"/>

--- a/excel/Grille de compétence  - BTS SIO 2026 (4).xlsx
+++ b/excel/Grille de compétence  - BTS SIO 2026 (4).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projet portfolio\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60EFA77-B4C4-499F-B384-16954B6D5449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E042BA19-78B6-4DBE-88DE-9343B5A1E4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -113,16 +113,10 @@
 </t>
   </si>
   <si>
-    <t>Projet GSB: création VLAN, Planifier taches, travail en groupe, DHCP, DNS, VLAN, VM Client/serveur, serveur messagerie, gestion des droits d'accès</t>
-  </si>
-  <si>
     <t>12/2026-07/2026</t>
   </si>
   <si>
     <t>X</t>
-  </si>
-  <si>
-    <t>Mise en place d'une veille techno (IA)</t>
   </si>
   <si>
     <t>2024-2026</t>
@@ -132,9 +126,6 @@
   </si>
   <si>
     <t>10/2024-04/2025</t>
-  </si>
-  <si>
-    <t>Créer plusieurs VM</t>
   </si>
   <si>
     <t>2025-2026</t>
@@ -147,9 +138,6 @@
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de première année</t>
-  </si>
-  <si>
-    <t>Maintenance et remise en état des postes clients du parc pédagogique.</t>
   </si>
   <si>
     <t>05/2025-07/2026</t>
@@ -191,16 +179,28 @@
     <t>Interventions de support de proximité auprès du corps enseignant.</t>
   </si>
   <si>
-    <t>Mise à jour de la documentation technique du parc informatique sur GLPI.</t>
-  </si>
-  <si>
     <t>01/2026-02/2026</t>
   </si>
   <si>
-    <t>Formater un disque dur système</t>
+    <t>Adresse URL du portfolio : https://amaraybk.github.io/Portfolio-Amara/#bts</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : https://amaraybk.github.io/Portfolio-Amara/#bts</t>
+    <t>Maintenance et remise en état des postes clients du parc pédagogique (remplacement des souris, clavier, cables, etc)</t>
+  </si>
+  <si>
+    <t>Projet GSB: création VLAN, Planifier taches, travail en groupe, DHCP, DNS, VLAN, VM Client/serveur, serveur messagerie, gestion des droits d'accès, etc.</t>
+  </si>
+  <si>
+    <t>Mise en place d'une veille techno (IA dans l'automobile)</t>
+  </si>
+  <si>
+    <t>Créer plusieurs VM (VMWare, VirtualBox)</t>
+  </si>
+  <si>
+    <t>Formater un disque dur système (NTFS)</t>
+  </si>
+  <si>
+    <t>Rédaction et mise à jour de tickets GLPI pour documenter les pannes rencontrées et assurer le suivi des interventions selon les directives du technicien référent.</t>
   </si>
 </sst>
 </file>
@@ -687,7 +687,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -777,6 +777,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -790,6 +796,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -810,16 +821,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1050,56 +1053,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="38" t="s">
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="39"/>
+      <c r="H1" s="41"/>
     </row>
     <row r="2" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
     </row>
     <row r="3" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="48" t="s">
+      <c r="A3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="49"/>
-      <c r="F3" s="40" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="41"/>
-      <c r="H3" s="42"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="47"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="34"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="37"/>
+      <c r="B4" s="36"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1111,22 +1114,22 @@
       </c>
     </row>
     <row r="5" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="50" t="s">
-        <v>53</v>
+      <c r="A5" s="42" t="s">
+        <v>47</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="52"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="s">
+      <c r="A6" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="48" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1149,8 +1152,8 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="324.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="47"/>
-      <c r="B7" s="44"/>
+      <c r="A7" s="52"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
@@ -1171,45 +1174,45 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="45" t="s">
+      <c r="A8" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="47"/>
     </row>
     <row r="9" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="C9" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
       <c r="F9" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="B10" s="31" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
@@ -1217,18 +1220,18 @@
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
       <c r="H10" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11"/>
@@ -1238,13 +1241,13 @@
     </row>
     <row r="12" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="B12" s="31" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11"/>
@@ -1254,19 +1257,19 @@
     </row>
     <row r="13" spans="1:13" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11"/>
       <c r="F13" s="11"/>
       <c r="G13" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H13" s="12"/>
     </row>
@@ -1311,29 +1314,29 @@
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="33" t="s">
-        <v>35</v>
+      <c r="A18" s="35" t="s">
+        <v>32</v>
       </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="35"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="37"/>
     </row>
     <row r="19" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="9" t="s">
-        <v>36</v>
+      <c r="A19" s="55" t="s">
+        <v>48</v>
       </c>
-      <c r="B19" s="53" t="s">
-        <v>37</v>
+      <c r="B19" s="33" t="s">
+        <v>33</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" s="11"/>
       <c r="F19" s="16"/>
@@ -1342,49 +1345,49 @@
     </row>
     <row r="20" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
-      <c r="B20" s="54" t="s">
-        <v>39</v>
+      <c r="B20" s="34" t="s">
+        <v>35</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="11"/>
       <c r="F20" s="16"/>
       <c r="G20" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H20" s="17"/>
     </row>
     <row r="21" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
-      <c r="B21" s="53" t="s">
-        <v>41</v>
+      <c r="B21" s="33" t="s">
+        <v>37</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="11"/>
       <c r="E21" s="11"/>
       <c r="F21" s="16"/>
       <c r="G21" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
-      <c r="B22" s="54" t="s">
-        <v>43</v>
+      <c r="B22" s="34" t="s">
+        <v>39</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22" s="11"/>
       <c r="E22" s="11"/>
@@ -1394,16 +1397,16 @@
     </row>
     <row r="23" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="11"/>
       <c r="F23" s="16"/>
@@ -1431,29 +1434,29 @@
       <c r="H25" s="17"/>
     </row>
     <row r="26" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="33" t="s">
-        <v>46</v>
+      <c r="A26" s="35" t="s">
+        <v>42</v>
       </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="35"/>
+      <c r="B26" s="36"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="36"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="37"/>
     </row>
     <row r="27" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
-      <c r="B27" s="53" t="s">
-        <v>48</v>
+      <c r="B27" s="33" t="s">
+        <v>44</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
@@ -1462,49 +1465,49 @@
     </row>
     <row r="28" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
-      <c r="B28" s="54">
+      <c r="B28" s="34">
         <v>46023</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="11"/>
       <c r="F28" s="11"/>
       <c r="G28" s="16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H28" s="17"/>
     </row>
     <row r="29" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="9" t="s">
-        <v>50</v>
+      <c r="A29" s="55" t="s">
+        <v>53</v>
       </c>
-      <c r="B29" s="53" t="s">
-        <v>51</v>
+      <c r="B29" s="33" t="s">
+        <v>46</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="11"/>
       <c r="F29" s="11"/>
       <c r="G29" s="11"/>
       <c r="H29" s="17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B30" s="54">
+      <c r="B30" s="34">
         <v>46023</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="11"/>
